--- a/U盘目录/任务表.xlsx
+++ b/U盘目录/任务表.xlsx
@@ -62,7 +62,7 @@
     <t>david.lee@example.com</t>
   </si>
   <si>
-    <t>sue.s@pak-eco.com</t>
+    <t>sue@pak-eco.com</t>
   </si>
   <si>
     <t>PACK EXPO 2026 is coming — and we'd love to see you there!
